--- a/data/TTC/最新版班表/TTC_TM.xlsx
+++ b/data/TTC/最新版班表/TTC_TM.xlsx
@@ -1141,10 +1141,10 @@
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CM0004
-13:56
-8:16</t>
+          <t>6:41
+CM0011
+14:59
+8:18</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1154,10 +1154,10 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>13:08
-CM0509
-21:14
-8:06</t>
+          <t>15:17
+CM0518
+23:42
+8:25</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1170,10 +1170,10 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>13:14
-CM0517
-23:03
-9:49</t>
+          <t>16:08
+CM0514
+24:08
+8:00</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr">
@@ -1402,9 +1402,9 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>8:13
-CM0015
-16:13
+          <t>5:15
+CM0001
+13:15
 8:00</t>
         </is>
       </c>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="AB8" s="1" t="inlineStr">
         <is>
-          <t>16:31
-CM2525
-24:31
-8:00</t>
+          <t>6:02
+CM1008
+14:40
+8:38</t>
         </is>
       </c>
       <c r="AC8" s="1" t="inlineStr">
         <is>
-          <t>16:01
-CM1522
-24:01
+          <t>5:40
+CM2004
+13:40
 8:00</t>
         </is>
       </c>
       <c r="AD8" s="1" t="inlineStr">
         <is>
-          <t>16:08
-CM0527
-24:08
+          <t>13:08
+CM0508
+21:08
 8:00</t>
         </is>
       </c>
@@ -1800,10 +1800,10 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>11:13
-CM0025
-21:04
-9:51</t>
+          <t>10:40
+CM0020
+19:14
+8:34</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1813,18 +1813,18 @@
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>13:20
-CM0512
-21:59
-8:39</t>
+          <t>5:40
+CM0004
+13:56
+8:16</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>13:56
-CM0511
-21:56
-8:00</t>
+          <t>5:35
+CM0002
+14:40
+9:05</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2008,33 +2008,33 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="inlineStr">
-        <is>
-          <t>15:14
-CM0524
-24:31
-9:17</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr">
         <is>
-          <t>15:20
-CM0523
-24:31
-9:11</t>
+          <t>6:02
+CM2008
+14:02
+8:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CM0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>DO1</t>
+          <t>5:35
+CM0002
+14:40
+9:05</t>
+        </is>
+      </c>
+      <c r="T11" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CM0503
+20:37
+8:00</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -2187,34 +2187,34 @@
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>16:20
-CM0525
-24:31
-8:11</t>
+          <t>6:02
+CM0008
+14:20
+8:18</t>
         </is>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
-          <t>15:20
-CM0523
-24:31
-9:11</t>
+          <t>5:40
+CM0004
+13:56
+8:16</t>
         </is>
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>15:40
-CM0522
-24:01
-8:21</t>
+          <t>12:37
+CM0503
+20:37
+8:00</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>15:17
-CM0518
-23:42
-8:25</t>
+          <t>13:08
+CM0509
+21:14
+8:06</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -3033,67 +3033,67 @@
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
+          <t>13:20
+CM0512
+21:59
+8:39</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="inlineStr">
+        <is>
+          <t>13:56
+CM0511
+21:56
+8:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="O16" s="1" t="inlineStr">
+        <is>
+          <t>12:04
+CM0507
+21:00
+8:56</t>
+        </is>
+      </c>
+      <c r="P16" s="1" t="inlineStr">
+        <is>
+          <t>12:20
+CM0502
+20:20
+8:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
           <t>6:02
 CM0008
 14:20
 8:18</t>
         </is>
       </c>
-      <c r="M16" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CM0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="O16" s="1" t="inlineStr">
-        <is>
-          <t>12:04
-CM0507
-21:00
-8:56</t>
-        </is>
-      </c>
-      <c r="P16" s="1" t="inlineStr">
-        <is>
-          <t>12:20
-CM0502
-20:20
-8:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="R16" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CM0008
-14:20
-8:18</t>
-        </is>
-      </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CM0001
-13:15
+          <t>8:13
+CM0015
+16:13
 8:00</t>
         </is>
       </c>
@@ -3357,17 +3357,17 @@
       </c>
       <c r="AB17" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CM1008
-14:40
-8:38</t>
+          <t>16:31
+CM2525
+24:31
+8:00</t>
         </is>
       </c>
       <c r="AC17" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CM2004
-13:40
+          <t>16:01
+CM1522
+24:01
 8:00</t>
         </is>
       </c>
@@ -3550,26 +3550,26 @@
       </c>
       <c r="Y18" s="1" t="inlineStr">
         <is>
-          <t>9:37
-CM5903
-18:08
-8:31</t>
+          <t>7:00
+CM1012
+15:00
+8:00</t>
         </is>
       </c>
       <c r="Z18" s="1" t="inlineStr">
         <is>
-          <t>8:19
-CM5901
-16:19
+          <t>5:50
+CM0007
+13:50
 8:00</t>
         </is>
       </c>
       <c r="AA18" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CM0008
-14:20
-8:18</t>
+          <t>5:15
+CM0001
+13:20
+8:05</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -4492,10 +4492,10 @@
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>6:02
+          <t>7:14
 DO2W
-CM0009
-14:02
+CM2011
+15:14
 8:00</t>
         </is>
       </c>
@@ -4919,10 +4919,10 @@
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>7:14
+          <t>6:02
 DO2W
-CM2011
-15:14
+CM0009
+14:02
 8:00</t>
         </is>
       </c>
@@ -5027,6 +5027,429 @@
         </is>
       </c>
       <c r="X25" s="1" t="inlineStr">
+        <is>
+          <t>13:17
+DO2W
+CM0517
+23:03
+9:46</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Z25" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AA25" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AB25" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AC25" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A022312</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>洪詩雯</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>7:42
+CM1014
+15:42
+8:00</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>5:00
+STD1
+13:00
+8:00</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CM0006
+13:59
+8:15</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>16:08
+CM2523
+24:31
+8:23</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+DO2W
+CM5903
+24:28
+9:11</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr">
+        <is>
+          <t>15:17
+CM0524
+24:31
+9:14</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CM1503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="N26" s="1" t="inlineStr">
+        <is>
+          <t>7:42
+CM0014
+15:42
+8:00</t>
+        </is>
+      </c>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CM0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="P26" s="1" t="inlineStr">
+        <is>
+          <t>5:44
+CM2006
+13:52
+8:08</t>
+        </is>
+      </c>
+      <c r="Q26" s="1" t="inlineStr">
+        <is>
+          <t>11:13
+CM0025
+21:04
+9:51</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="S26" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CM0022
+19:52
+9:00</t>
+        </is>
+      </c>
+      <c r="T26" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CM0022
+19:52
+9:00</t>
+        </is>
+      </c>
+      <c r="U26" s="1" t="inlineStr">
+        <is>
+          <t>10:56
+CM1022
+19:52
+8:56</t>
+        </is>
+      </c>
+      <c r="V26" s="1" t="inlineStr">
+        <is>
+          <t>10:20
+CM0019
+19:14
+8:54</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="Y26" s="1" t="inlineStr">
+        <is>
+          <t>6:02
+CM2008
+14:56
+8:54</t>
+        </is>
+      </c>
+      <c r="Z26" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CM0002
+14:40
+9:05</t>
+        </is>
+      </c>
+      <c r="AA26" s="1" t="inlineStr">
+        <is>
+          <t>5:40
+CM0004
+13:56
+8:16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="AC26" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CM0011
+14:59
+8:18</t>
+        </is>
+      </c>
+      <c r="AD26" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CM0001
+13:15
+8:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A022348</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>徐尉晞</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>5:35
+CM2003
+13:40
+8:05</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>5:15
+CM0001
+13:15
+8:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>DO2</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="L27" s="1" t="inlineStr">
+        <is>
+          <t>8:30
+PAY
+17:30
+8:00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>16:14
+CM1526
+24:31
+8:17</t>
+        </is>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>16:31
+CM3523
+24:31
+8:00</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
+          <t>15:40
+CM0522
+24:01
+8:21</t>
+        </is>
+      </c>
+      <c r="R27" s="1" t="inlineStr">
+        <is>
+          <t>15:52
+CM1525
+24:31
+8:39</t>
+        </is>
+      </c>
+      <c r="S27" s="1" t="inlineStr">
+        <is>
+          <t>16:30
+STD8
+24:30
+8:00</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="U27" s="1" t="inlineStr">
+        <is>
+          <t>12:37
+CM0503
+20:37
+8:00</t>
+        </is>
+      </c>
+      <c r="V27" s="1" t="inlineStr">
+        <is>
+          <t>12:40
+CM0504
+20:40
+8:00</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
+        </is>
+      </c>
+      <c r="X27" s="1" t="inlineStr">
         <is>
           <t>13:56
 DO2W
@@ -5035,429 +5458,6 @@
 9:46</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Z25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC25" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A022312</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>洪詩雯</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>7:42
-CM1014
-15:42
-8:00</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>5:00
-STD1
-13:00
-8:00</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CM0006
-13:59
-8:15</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>16:08
-CM2523
-24:31
-8:23</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-DO2W
-CM5903
-24:28
-9:11</t>
-        </is>
-      </c>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>15:17
-CM0524
-24:31
-9:14</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CM1503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>7:42
-CM0014
-15:42
-8:00</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CM0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t>5:44
-CM2006
-13:52
-8:08</t>
-        </is>
-      </c>
-      <c r="Q26" s="1" t="inlineStr">
-        <is>
-          <t>10:40
-CM0020
-19:14
-8:34</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="S26" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CM0022
-19:52
-9:00</t>
-        </is>
-      </c>
-      <c r="T26" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CM0022
-19:52
-9:00</t>
-        </is>
-      </c>
-      <c r="U26" s="1" t="inlineStr">
-        <is>
-          <t>10:56
-CM1022
-19:52
-8:56</t>
-        </is>
-      </c>
-      <c r="V26" s="1" t="inlineStr">
-        <is>
-          <t>10:20
-CM0019
-19:14
-8:54</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="Y26" s="1" t="inlineStr">
-        <is>
-          <t>6:02
-CM2008
-14:56
-8:54</t>
-        </is>
-      </c>
-      <c r="Z26" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CM0002
-14:40
-9:05</t>
-        </is>
-      </c>
-      <c r="AA26" s="1" t="inlineStr">
-        <is>
-          <t>5:40
-CM0004
-13:56
-8:16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AC26" s="1" t="inlineStr">
-        <is>
-          <t>6:41
-CM0011
-14:59
-8:18</t>
-        </is>
-      </c>
-      <c r="AD26" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CM0001
-13:15
-8:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A022348</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>徐尉晞</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>5:35
-CM2003
-13:40
-8:05</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>5:15
-CM0001
-13:15
-8:00</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>DO2</t>
-        </is>
-      </c>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L27" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="O27" s="1" t="inlineStr">
-        <is>
-          <t>16:14
-CM1526
-24:31
-8:17</t>
-        </is>
-      </c>
-      <c r="P27" s="1" t="inlineStr">
-        <is>
-          <t>16:31
-CM3523
-24:31
-8:00</t>
-        </is>
-      </c>
-      <c r="Q27" s="1" t="inlineStr">
-        <is>
-          <t>15:40
-CM0522
-24:01
-8:21</t>
-        </is>
-      </c>
-      <c r="R27" s="1" t="inlineStr">
-        <is>
-          <t>15:52
-CM1525
-24:31
-8:39</t>
-        </is>
-      </c>
-      <c r="S27" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD8
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="U27" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CM0503
-20:37
-8:00</t>
-        </is>
-      </c>
-      <c r="V27" s="1" t="inlineStr">
-        <is>
-          <t>12:40
-CM0504
-20:40
-8:00</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="X27" s="1" t="inlineStr">
-        <is>
-          <t>13:17
-DO2W
-CM0517
-23:03
-9:46</t>
-        </is>
-      </c>
       <c r="Y27" s="1" t="inlineStr">
         <is>
           <t>13:00
@@ -6229,10 +6229,10 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>5:15
-CM0001
-13:15
-8:00</t>
+          <t>6:02
+CM1008
+14:40
+8:38</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -6625,26 +6625,26 @@
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
-          <t>13:20
-CM0512
-21:59
-8:39</t>
+          <t>16:20
+CM0525
+24:31
+8:11</t>
         </is>
       </c>
       <c r="M33" s="1" t="inlineStr">
         <is>
-          <t>13:56
-CM0511
-21:56
-8:00</t>
+          <t>15:20
+CM0523
+24:31
+9:11</t>
         </is>
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>12:37
-CM0503
-20:37
-8:00</t>
+          <t>15:40
+CM0522
+24:01
+8:21</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -6660,33 +6660,33 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Q33" s="1" t="inlineStr">
+        <is>
+          <t>15:14
+CM0524
+24:31
+9:17</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CM2008
-14:02
+          <t>16:30
+STD8
+24:30
 8:00</t>
         </is>
       </c>
       <c r="S33" s="1" t="inlineStr">
         <is>
-          <t>5:35
-CM0002
-14:40
-9:05</t>
-        </is>
-      </c>
-      <c r="T33" s="1" t="inlineStr">
-        <is>
-          <t>12:37
-CM0503
-20:37
-8:00</t>
+          <t>15:40
+CM0522
+24:01
+8:21</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="U33" s="1" t="inlineStr">
@@ -6968,9 +6968,9 @@
       </c>
       <c r="AD34" s="1" t="inlineStr">
         <is>
-          <t>13:08
-CM0508
-21:08
+          <t>16:08
+CM0527
+24:08
 8:00</t>
         </is>
       </c>
@@ -7089,26 +7089,13 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>16:08
-CM0514
-24:08
-8:00</t>
+          <t>13:14
+CM0517
+23:03
+9:49</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr">
-        <is>
-          <t>16:30
-STD8
-24:30
-8:00</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>DO1</t>
-        </is>
-      </c>
-      <c r="T35" s="1" t="inlineStr">
         <is>
           <t>15:20
 CM0523
@@ -7116,6 +7103,19 @@
 9:11</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="T35" s="1" t="inlineStr">
+        <is>
+          <t>15:20
+CM0523
+24:31
+9:11</t>
+        </is>
+      </c>
       <c r="U35" s="1" t="inlineStr">
         <is>
           <t>15:20
@@ -7280,10 +7280,10 @@
       </c>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>6:02
-CM1008
-14:40
-8:38</t>
+          <t>5:15
+CM0001
+13:15
+8:00</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">

--- a/data/TTC/最新版班表/TTC_TM.xlsx
+++ b/data/TTC/最新版班表/TTC_TM.xlsx
@@ -3091,10 +3091,10 @@
       </c>
       <c r="T16" s="1" t="inlineStr">
         <is>
-          <t>8:13
-CM0015
-16:13
-8:00</t>
+          <t>5:40
+CM0004
+13:56
+8:16</t>
         </is>
       </c>
       <c r="U16" s="1" t="inlineStr">
@@ -4841,10 +4841,10 @@
       </c>
       <c r="AB24" s="1" t="inlineStr">
         <is>
-          <t>6:41
-CM0011
-14:59
-8:18</t>
+          <t>7:42
+CM0014
+15:42
+8:00</t>
         </is>
       </c>
       <c r="AC24" s="1" t="inlineStr">
@@ -5466,22 +5466,22 @@
 8:14</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="Z27" s="1" t="inlineStr">
+        <is>
+          <t>10:52
+CM0022
+19:52
+9:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>DO3X</t>
-        </is>
-      </c>
-      <c r="AB27" s="1" t="inlineStr">
-        <is>
-          <t>7:42
-CM0014
-15:42
-8:00</t>
+          <t>DO1</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>DO3X</t>
         </is>
       </c>
       <c r="AC27" s="1" t="inlineStr">
@@ -6001,10 +6001,10 @@
       </c>
       <c r="K30" s="1" t="inlineStr">
         <is>
-          <t>10:52
-CM0022
-19:52
-9:00</t>
+          <t>11:45
+CM0026
+19:45
+8:00</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -7153,12 +7153,9 @@
 9:44</t>
         </is>
       </c>
-      <c r="Z35" s="1" t="inlineStr">
-        <is>
-          <t>10:52
-CM0022
-19:52
-9:00</t>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>DO1</t>
         </is>
       </c>
       <c r="AA35" s="1" t="inlineStr">
@@ -7169,9 +7166,12 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>DO1</t>
+      <c r="AB35" s="1" t="inlineStr">
+        <is>
+          <t>6:41
+CM0011
+14:59
+8:18</t>
         </is>
       </c>
       <c r="AC35" s="1" t="inlineStr">
@@ -7322,10 +7322,10 @@
       </c>
       <c r="T36" s="1" t="inlineStr">
         <is>
-          <t>5:40
-CM0004
-13:56
-8:16</t>
+          <t>8:13
+CM0015
+16:13
+8:00</t>
         </is>
       </c>
       <c r="U36" s="1" t="inlineStr">
